--- a/output/yearly_benthic_cover_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_12_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.27691223042534</v>
+        <v>45.77107466610484</v>
       </c>
       <c r="M2" t="n">
-        <v>101.7729889248945</v>
+        <v>98.85707481536619</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03892748392289</v>
+        <v>88.10752219601862</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92241781861946</v>
+        <v>45.94664203416021</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228765168037302</v>
+        <v>2.228922602821689</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703446542872682</v>
+        <v>5.721063193059601</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429217226791005</v>
+        <v>0.7429742009405631</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97081876065866</v>
+        <v>33.97850206721848</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17439924323862</v>
+        <v>34.1768132432659</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575315279692169</v>
+        <v>6.615658132833877</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643260766744378</v>
+        <v>4.643588755878519</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96107251607709</v>
+        <v>11.89247780398137</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8804932244872</v>
+        <v>48.9234324147017</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639835591838</v>
+        <v>106.7625522528433</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05915732755055</v>
+        <v>87.34495746136308</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57942027116596</v>
+        <v>42.82773873672281</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18122868272331</v>
+        <v>2.192998515919203</v>
       </c>
       <c r="E4" t="n">
-        <v>6.496958108229109</v>
+        <v>6.549634095747379</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444836282482461</v>
+        <v>0.7445406675453249</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24626807659426</v>
+        <v>33.43086229743294</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24624689941932</v>
+        <v>34.24887070708494</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490949255784749</v>
+        <v>5.52467200547501</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653022676551538</v>
+        <v>4.653379172158281</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94084267244946</v>
+        <v>12.65504253863694</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29708940972647</v>
+        <v>44.33345044317264</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81735235334189</v>
+        <v>99.81623171853238</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.89851257883353</v>
+        <v>86.26954375343495</v>
       </c>
       <c r="C5" t="n">
-        <v>42.27092558815914</v>
+        <v>42.60993742503268</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124615714931371</v>
+        <v>2.140885973076354</v>
       </c>
       <c r="E5" t="n">
-        <v>7.092320434033142</v>
+        <v>7.162677138230824</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458079279505579</v>
+        <v>0.7458674758075152</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38337372776677</v>
+        <v>32.63643985204513</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30716468572567</v>
+        <v>34.3099038871457</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583930538735043</v>
+        <v>4.612097703332457</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661299549690987</v>
+        <v>4.661671723796971</v>
       </c>
       <c r="K5" t="n">
-        <v>14.10148742116647</v>
+        <v>13.73045624656507</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47506062245814</v>
+        <v>43.50614321713906</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84747363178376</v>
+        <v>99.84653688873681</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.53367968321629</v>
+        <v>85.13719276629013</v>
       </c>
       <c r="C6" t="n">
-        <v>41.61794192833335</v>
+        <v>42.19408857747784</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058010756205609</v>
+        <v>2.086222869807796</v>
       </c>
       <c r="E6" t="n">
-        <v>7.507599459756633</v>
+        <v>7.621327467394912</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469330183306901</v>
+        <v>0.7469915432192316</v>
       </c>
       <c r="G6" t="n">
-        <v>31.36818154247855</v>
+        <v>31.80313574132368</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35891884321175</v>
+        <v>34.36161098808466</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825704698666256</v>
+        <v>3.849207011339641</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668331364566814</v>
+        <v>4.668697145120198</v>
       </c>
       <c r="K6" t="n">
-        <v>15.46632031678371</v>
+        <v>14.86280723370989</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78840635102919</v>
+        <v>42.81499036371972</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87266859614624</v>
+        <v>99.87188617490744</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.02168980250387</v>
+        <v>83.84249699868835</v>
       </c>
       <c r="C7" t="n">
-        <v>40.7000827708738</v>
+        <v>41.49759393905212</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984533333064514</v>
+        <v>2.02373553445629</v>
       </c>
       <c r="E7" t="n">
-        <v>7.771583552515854</v>
+        <v>7.928345322585465</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478903342818845</v>
+        <v>0.7479453808403962</v>
       </c>
       <c r="G7" t="n">
-        <v>30.24823931602834</v>
+        <v>30.85055620772829</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40295537696669</v>
+        <v>34.40548751865823</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192173300384812</v>
+        <v>3.2117684041672</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674314589261779</v>
+        <v>4.674658630252477</v>
       </c>
       <c r="K7" t="n">
-        <v>16.97831019749614</v>
+        <v>16.15750300131166</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2153374566671</v>
+        <v>42.23798064265456</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89373042503703</v>
+        <v>99.89307758301834</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.84276729330631</v>
+        <v>88.75195835595071</v>
       </c>
       <c r="C8" t="n">
-        <v>42.92965520828599</v>
+        <v>43.82372891512118</v>
       </c>
       <c r="D8" t="n">
-        <v>1.988795455786062</v>
+        <v>2.028046273876068</v>
       </c>
       <c r="E8" t="n">
-        <v>9.557426495959405</v>
+        <v>9.778975206961604</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494965559229424</v>
+        <v>0.749538572036644</v>
       </c>
       <c r="G8" t="n">
-        <v>30.72613543361086</v>
+        <v>31.3605173618604</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47684157245536</v>
+        <v>34.47877431368563</v>
       </c>
       <c r="I8" t="n">
-        <v>5.659718305053301</v>
+        <v>5.671490552301337</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684353474518391</v>
+        <v>4.684616075229026</v>
       </c>
       <c r="K8" t="n">
-        <v>12.15723270669371</v>
+        <v>11.2480416440493</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72485911344638</v>
+        <v>44.73958159270312</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81174702842607</v>
+        <v>99.81135215187359</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.92782220255293</v>
+        <v>86.96753908395141</v>
       </c>
       <c r="C9" t="n">
-        <v>41.89298083733884</v>
+        <v>42.92036516388839</v>
       </c>
       <c r="D9" t="n">
-        <v>1.902182930930527</v>
+        <v>1.947741123806374</v>
       </c>
       <c r="E9" t="n">
-        <v>9.928711080219387</v>
+        <v>10.1808907634055</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508703557872546</v>
+        <v>0.7508988227257328</v>
       </c>
       <c r="G9" t="n">
-        <v>29.38800477707921</v>
+        <v>30.11872565057257</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54003636621372</v>
+        <v>34.54134584538372</v>
       </c>
       <c r="I9" t="n">
-        <v>4.725076968652468</v>
+        <v>4.734819236021681</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692939723670343</v>
+        <v>4.693117642035831</v>
       </c>
       <c r="K9" t="n">
-        <v>14.07217779744709</v>
+        <v>13.03246091604858</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8776269678515</v>
+        <v>43.88963251583243</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84278560263743</v>
+        <v>99.84245859576941</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.83436743424036</v>
+        <v>85.02453619660915</v>
       </c>
       <c r="C10" t="n">
-        <v>40.53257506579446</v>
+        <v>41.71286725594869</v>
       </c>
       <c r="D10" t="n">
-        <v>1.808404771608165</v>
+        <v>1.861041154009848</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09651255221546</v>
+        <v>10.38634049709519</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520477712182422</v>
+        <v>0.7520621726771326</v>
       </c>
       <c r="G10" t="n">
-        <v>27.93916778598968</v>
+        <v>28.77804820001314</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59419747603915</v>
+        <v>34.59485994314811</v>
       </c>
       <c r="I10" t="n">
-        <v>3.943738507055661</v>
+        <v>3.951795650433636</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700298570114016</v>
+        <v>4.700388579232079</v>
       </c>
       <c r="K10" t="n">
-        <v>16.16563256575963</v>
+        <v>14.97546380339087</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17054023042778</v>
+        <v>43.18014618410428</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86874786198189</v>
+        <v>99.86847724344383</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.56176399013547</v>
+        <v>82.90452165725711</v>
       </c>
       <c r="C11" t="n">
-        <v>38.87127089623994</v>
+        <v>40.20633799144797</v>
       </c>
       <c r="D11" t="n">
-        <v>1.707551514727347</v>
+        <v>1.767210623538631</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08191643308534</v>
+        <v>10.41226707513799</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530592298756869</v>
+        <v>0.7530592823431654</v>
       </c>
       <c r="G11" t="n">
-        <v>26.38102322123554</v>
+        <v>27.32710794395516</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64072457428161</v>
+        <v>34.64072698778562</v>
       </c>
       <c r="I11" t="n">
-        <v>3.290868830206908</v>
+        <v>3.297529229851757</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706620186723045</v>
+        <v>4.706620514644785</v>
       </c>
       <c r="K11" t="n">
-        <v>18.43823600986452</v>
+        <v>17.09547834274289</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58094480203288</v>
+        <v>42.58841156440822</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89045170813735</v>
+        <v>99.89022789859908</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.11651893837775</v>
+        <v>80.65813119359737</v>
       </c>
       <c r="C12" t="n">
-        <v>36.93537046247272</v>
+        <v>38.47124463212793</v>
       </c>
       <c r="D12" t="n">
-        <v>1.600012514564221</v>
+        <v>1.668619909435953</v>
       </c>
       <c r="E12" t="n">
-        <v>9.904566482909418</v>
+        <v>10.28988915285964</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539303381133768</v>
+        <v>0.7539154535989646</v>
       </c>
       <c r="G12" t="n">
-        <v>24.71958645869964</v>
+        <v>25.80255900187111</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68079555321534</v>
+        <v>34.68011086555239</v>
       </c>
       <c r="I12" t="n">
-        <v>2.745562977667151</v>
+        <v>2.751065225285774</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712064613208607</v>
+        <v>4.711971584993529</v>
       </c>
       <c r="K12" t="n">
-        <v>20.88348106162223</v>
+        <v>19.34186880640265</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08973545284374</v>
+        <v>42.09528852730686</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90858697693869</v>
+        <v>99.90840196583744</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.65037638318196</v>
+        <v>78.27948155444928</v>
       </c>
       <c r="C13" t="n">
-        <v>34.89328143043353</v>
+        <v>36.51842627101841</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492568678913591</v>
+        <v>1.56503783881307</v>
       </c>
       <c r="E13" t="n">
-        <v>9.621164285159075</v>
+        <v>10.03359469566179</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546812313054346</v>
+        <v>0.7546521647916034</v>
       </c>
       <c r="G13" t="n">
-        <v>23.0596199517855</v>
+        <v>24.20082665187994</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71533664005</v>
+        <v>34.71399958041377</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2902479003094</v>
+        <v>2.294794592941586</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716757695658968</v>
+        <v>4.716576029947522</v>
       </c>
       <c r="K13" t="n">
-        <v>23.34962361681802</v>
+        <v>21.72051844555072</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68082931447991</v>
+        <v>41.68463680495073</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92373436173146</v>
+        <v>99.92358152151985</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.50119968637206</v>
+        <v>84.49427675912588</v>
       </c>
       <c r="C14" t="n">
-        <v>39.02919522213665</v>
+        <v>40.31604361177789</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494445904327893</v>
+        <v>1.566903148496847</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9489762407345</v>
+        <v>12.18052521164287</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556304049060323</v>
+        <v>0.7555516062977183</v>
       </c>
       <c r="G14" t="n">
-        <v>24.87923026070323</v>
+        <v>25.86111482001216</v>
       </c>
       <c r="H14" t="n">
-        <v>36.54960651398356</v>
+        <v>36.38681800358805</v>
       </c>
       <c r="I14" t="n">
-        <v>3.150620331054129</v>
+        <v>3.021166429727505</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722690030662704</v>
+        <v>4.72219753936074</v>
       </c>
       <c r="K14" t="n">
-        <v>16.49880031362794</v>
+        <v>15.50572324087412</v>
       </c>
       <c r="L14" t="n">
-        <v>44.36711570665506</v>
+        <v>44.07764748395603</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89511124241965</v>
+        <v>99.89941433660803</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.67177995591616</v>
+        <v>83.68295063885927</v>
       </c>
       <c r="C15" t="n">
-        <v>38.68644923730664</v>
+        <v>39.97237511475625</v>
       </c>
       <c r="D15" t="n">
-        <v>1.463650948181531</v>
+        <v>1.53634803254179</v>
       </c>
       <c r="E15" t="n">
-        <v>12.14080228875018</v>
+        <v>12.36302872029298</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564311710427158</v>
+        <v>0.7563100704298993</v>
       </c>
       <c r="G15" t="n">
-        <v>24.36656211887566</v>
+        <v>25.35681475346971</v>
       </c>
       <c r="H15" t="n">
-        <v>36.58833932173651</v>
+        <v>36.42334508672821</v>
       </c>
       <c r="I15" t="n">
-        <v>2.628299288312601</v>
+        <v>2.520166035209796</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727694819016976</v>
+        <v>4.726937940186872</v>
       </c>
       <c r="K15" t="n">
-        <v>17.32822004408382</v>
+        <v>16.31704936114073</v>
       </c>
       <c r="L15" t="n">
-        <v>43.89781348719137</v>
+        <v>43.62665423438838</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91248276858184</v>
+        <v>99.91607871028536</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.11438609121552</v>
+        <v>81.24373956279581</v>
       </c>
       <c r="C16" t="n">
-        <v>36.53509422997059</v>
+        <v>37.92331356111673</v>
       </c>
       <c r="D16" t="n">
-        <v>1.366317410743453</v>
+        <v>1.442128593572894</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69880725447062</v>
+        <v>11.95516760284569</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571211362289559</v>
+        <v>0.7569623158037474</v>
       </c>
       <c r="G16" t="n">
-        <v>22.74617326237852</v>
+        <v>23.80176029347374</v>
       </c>
       <c r="H16" t="n">
-        <v>36.6217127221472</v>
+        <v>36.45475675141672</v>
       </c>
       <c r="I16" t="n">
-        <v>2.192247203815785</v>
+        <v>2.101949531909582</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732007101430976</v>
+        <v>4.731014473773422</v>
       </c>
       <c r="K16" t="n">
-        <v>19.88561390878451</v>
+        <v>18.75626043720419</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50628354768065</v>
+        <v>43.25042138958992</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92699168643574</v>
+        <v>99.92999538791084</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.76859170296321</v>
+        <v>82.70033899663272</v>
       </c>
       <c r="C17" t="n">
-        <v>37.72844815127218</v>
+        <v>38.99528768226419</v>
       </c>
       <c r="D17" t="n">
-        <v>1.36755351668056</v>
+        <v>1.443353135030446</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47487033464977</v>
+        <v>12.66095111105881</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578061029315996</v>
+        <v>0.7576050682889541</v>
       </c>
       <c r="G17" t="n">
-        <v>23.1623510847206</v>
+        <v>24.16649007971871</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05044373057321</v>
+        <v>36.83023046077233</v>
       </c>
       <c r="I17" t="n">
-        <v>2.219278790084967</v>
+        <v>2.106677464957495</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736288143322499</v>
+        <v>4.735031676805964</v>
       </c>
       <c r="K17" t="n">
-        <v>18.2314082970368</v>
+        <v>17.29966100336728</v>
       </c>
       <c r="L17" t="n">
-        <v>43.966234457502</v>
+        <v>43.63488830907398</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92609090581097</v>
+        <v>99.92983699470545</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.40352221352448</v>
+        <v>80.28680062303532</v>
       </c>
       <c r="C18" t="n">
-        <v>35.70574471483337</v>
+        <v>36.90745511285473</v>
       </c>
       <c r="D18" t="n">
-        <v>1.28114432957329</v>
+        <v>1.353314812771329</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99511540499935</v>
+        <v>12.1639513547391</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583948991305135</v>
+        <v>0.7581576683505127</v>
       </c>
       <c r="G18" t="n">
-        <v>21.69883254280499</v>
+        <v>22.65895171723503</v>
       </c>
       <c r="H18" t="n">
-        <v>37.07923098941454</v>
+        <v>36.85709457305422</v>
       </c>
       <c r="I18" t="n">
-        <v>1.850835928036082</v>
+        <v>1.756845069694419</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739968119565711</v>
+        <v>4.738485427190706</v>
       </c>
       <c r="K18" t="n">
-        <v>20.59647778647553</v>
+        <v>19.71319937696468</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63613086563318</v>
+        <v>43.32082669170955</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93835336694208</v>
+        <v>99.94148118152896</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.47128404600284</v>
+        <v>79.26650950391976</v>
       </c>
       <c r="C19" t="n">
-        <v>35.05830955454706</v>
+        <v>36.15809069366021</v>
       </c>
       <c r="D19" t="n">
-        <v>1.247813798333122</v>
+        <v>1.315956962189546</v>
       </c>
       <c r="E19" t="n">
-        <v>11.94027693223473</v>
+        <v>12.07232569348242</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588921032235724</v>
+        <v>0.7586247235607274</v>
       </c>
       <c r="G19" t="n">
-        <v>21.13431096686044</v>
+        <v>22.03345813318208</v>
       </c>
       <c r="H19" t="n">
-        <v>37.10354015267045</v>
+        <v>36.87980000593755</v>
       </c>
       <c r="I19" t="n">
-        <v>1.54337444753319</v>
+        <v>1.464939463312904</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743075645147329</v>
+        <v>4.741404522254547</v>
       </c>
       <c r="K19" t="n">
-        <v>21.52871595399718</v>
+        <v>20.73349049608022</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36156238234365</v>
+        <v>43.0596175583236</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94858789088788</v>
+        <v>99.95119874806404</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.88071692637565</v>
+        <v>76.63939191726348</v>
       </c>
       <c r="C20" t="n">
-        <v>32.70508424318207</v>
+        <v>33.75671174010748</v>
       </c>
       <c r="D20" t="n">
-        <v>1.154284157354217</v>
+        <v>1.219003876942067</v>
       </c>
       <c r="E20" t="n">
-        <v>11.25977453265657</v>
+        <v>11.38646940484269</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593211087162773</v>
+        <v>0.7590277400130148</v>
       </c>
       <c r="G20" t="n">
-        <v>19.55019279177093</v>
+        <v>20.41014384095108</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1245149690596</v>
+        <v>36.89939225714932</v>
       </c>
       <c r="I20" t="n">
-        <v>1.286872437341314</v>
+        <v>1.221431422283966</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745756929476736</v>
+        <v>4.743923375081343</v>
       </c>
       <c r="K20" t="n">
-        <v>24.11928307362436</v>
+        <v>23.36060808273651</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1327611707621</v>
+        <v>42.84198741428619</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95712848756853</v>
+        <v>99.95930723713019</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.7756701039108</v>
+        <v>82.31619093743799</v>
       </c>
       <c r="C21" t="n">
-        <v>36.28269320260203</v>
+        <v>37.20995595325022</v>
       </c>
       <c r="D21" t="n">
-        <v>1.155197737786851</v>
+        <v>1.219911403300084</v>
       </c>
       <c r="E21" t="n">
-        <v>13.21146239506332</v>
+        <v>13.26708802590208</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599220880354417</v>
+        <v>0.7595928224492219</v>
       </c>
       <c r="G21" t="n">
-        <v>21.18482761820662</v>
+        <v>21.99106584139264</v>
       </c>
       <c r="H21" t="n">
-        <v>38.77305933133677</v>
+        <v>38.49259020506296</v>
       </c>
       <c r="I21" t="n">
-        <v>1.941687883260288</v>
+        <v>1.838487499023375</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749513050221513</v>
+        <v>4.747455140307638</v>
       </c>
       <c r="K21" t="n">
-        <v>18.22432989608918</v>
+        <v>17.68380906256201</v>
       </c>
       <c r="L21" t="n">
-        <v>45.42830515756423</v>
+        <v>45.04499765763666</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93532825625545</v>
+        <v>99.93876267344888</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_12_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.77107466610484</v>
+        <v>45.38539502757816</v>
       </c>
       <c r="M2" t="n">
-        <v>98.85707481536619</v>
+        <v>100.9651976429611</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10752219601862</v>
+        <v>87.92995348875149</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94664203416021</v>
+        <v>45.81838937750821</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228922602821689</v>
+        <v>2.228564356072622</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721063193059601</v>
+        <v>5.638287410281158</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429742009405631</v>
+        <v>0.7428547853575408</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97850206721848</v>
+        <v>33.93580570636004</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1768132432659</v>
+        <v>34.17132012644687</v>
       </c>
       <c r="I3" t="n">
-        <v>6.615658132833877</v>
+        <v>6.570278695748642</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643588755878519</v>
+        <v>4.64284240848463</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89247780398137</v>
+        <v>12.07004651124849</v>
       </c>
       <c r="L3" t="n">
-        <v>48.9234324147017</v>
+        <v>48.87570720442901</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7625522528433</v>
+        <v>106.7641430931857</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.34495746136308</v>
+        <v>86.91559721641936</v>
       </c>
       <c r="C4" t="n">
-        <v>42.82773873672281</v>
+        <v>42.44369469348207</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192998515919203</v>
+        <v>2.179063109709986</v>
       </c>
       <c r="E4" t="n">
-        <v>6.549634095747379</v>
+        <v>6.427507735370426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445406675453249</v>
+        <v>0.7444179344393389</v>
       </c>
       <c r="G4" t="n">
-        <v>33.43086229743294</v>
+        <v>33.18201788138312</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24887070708494</v>
+        <v>34.24322498420958</v>
       </c>
       <c r="I4" t="n">
-        <v>5.52467200547501</v>
+        <v>5.48675348106103</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653379172158281</v>
+        <v>4.652612090245868</v>
       </c>
       <c r="K4" t="n">
-        <v>12.65504253863694</v>
+        <v>13.08440278358064</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33345044317264</v>
+        <v>44.28939478138871</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81623171853238</v>
+        <v>99.81749225845142</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.26954375343495</v>
+        <v>85.70177608297827</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60993742503268</v>
+        <v>42.08123462205359</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140885973076354</v>
+        <v>2.119537820637717</v>
       </c>
       <c r="E5" t="n">
-        <v>7.162677138230824</v>
+        <v>7.01533474862184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458674758075152</v>
+        <v>0.7457441465148005</v>
       </c>
       <c r="G5" t="n">
-        <v>32.63643985204513</v>
+        <v>32.27558740785113</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3099038871457</v>
+        <v>34.30423073968082</v>
       </c>
       <c r="I5" t="n">
-        <v>4.612097703332457</v>
+        <v>4.580440303954457</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661671723796971</v>
+        <v>4.660900915717503</v>
       </c>
       <c r="K5" t="n">
-        <v>13.73045624656507</v>
+        <v>14.29822391702174</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50614321713906</v>
+        <v>43.46813164200631</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84653688873681</v>
+        <v>99.84759018108164</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.13719276629013</v>
+        <v>84.17232739430001</v>
       </c>
       <c r="C6" t="n">
-        <v>42.19408857747784</v>
+        <v>41.26292769938537</v>
       </c>
       <c r="D6" t="n">
-        <v>2.086222869807796</v>
+        <v>2.044345300716459</v>
       </c>
       <c r="E6" t="n">
-        <v>7.621327467394912</v>
+        <v>7.403594762568948</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469915432192316</v>
+        <v>0.7468731160376505</v>
       </c>
       <c r="G6" t="n">
-        <v>31.80313574132368</v>
+        <v>31.13058177242209</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36161098808466</v>
+        <v>34.35616333773192</v>
       </c>
       <c r="I6" t="n">
-        <v>3.849207011339641</v>
+        <v>3.822812129587634</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668697145120198</v>
+        <v>4.667956975235315</v>
       </c>
       <c r="K6" t="n">
-        <v>14.86280723370989</v>
+        <v>15.82767260569998</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81499036371972</v>
+        <v>42.78216524202703</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87188617490744</v>
+        <v>99.87276554711238</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.84249699868835</v>
+        <v>82.41576277271115</v>
       </c>
       <c r="C7" t="n">
-        <v>41.49759393905212</v>
+        <v>40.09977645926568</v>
       </c>
       <c r="D7" t="n">
-        <v>2.02373553445629</v>
+        <v>1.958372882985232</v>
       </c>
       <c r="E7" t="n">
-        <v>7.928345322585465</v>
+        <v>7.62387683841778</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479453808403962</v>
+        <v>0.7478366719712022</v>
       </c>
       <c r="G7" t="n">
-        <v>30.85055620772829</v>
+        <v>29.8214235889113</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40548751865823</v>
+        <v>34.4004869106753</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2117684041672</v>
+        <v>3.189786679930343</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674658630252477</v>
+        <v>4.673979199820013</v>
       </c>
       <c r="K7" t="n">
-        <v>16.15750300131166</v>
+        <v>17.58423722728883</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23798064265456</v>
+        <v>42.2097970876236</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89307758301834</v>
+        <v>99.89381077417812</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.75195835595071</v>
+        <v>87.17023194512251</v>
       </c>
       <c r="C8" t="n">
-        <v>43.82372891512118</v>
+        <v>42.41920636208909</v>
       </c>
       <c r="D8" t="n">
-        <v>2.028046273876068</v>
+        <v>1.962495414150058</v>
       </c>
       <c r="E8" t="n">
-        <v>9.778975206961604</v>
+        <v>9.460739570168862</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749538572036644</v>
+        <v>0.749410927830843</v>
       </c>
       <c r="G8" t="n">
-        <v>31.3605173618604</v>
+        <v>30.33585626369076</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47877431368563</v>
+        <v>34.47290268021877</v>
       </c>
       <c r="I8" t="n">
-        <v>5.671490552301337</v>
+        <v>5.505008790120442</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684616075229026</v>
+        <v>4.683818298942768</v>
       </c>
       <c r="K8" t="n">
-        <v>11.2480416440493</v>
+        <v>12.82976805487748</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73958159270312</v>
+        <v>44.56791076133864</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81135215187359</v>
+        <v>99.81688517830523</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.96753908395141</v>
+        <v>84.97822879287004</v>
       </c>
       <c r="C9" t="n">
-        <v>42.92036516388839</v>
+        <v>41.08108357777144</v>
       </c>
       <c r="D9" t="n">
-        <v>1.947741123806374</v>
+        <v>1.862832949828227</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1808907634055</v>
+        <v>9.746252615663209</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508988227257328</v>
+        <v>0.750761911416857</v>
       </c>
       <c r="G9" t="n">
-        <v>30.11872565057257</v>
+        <v>28.79529409434595</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54134584538372</v>
+        <v>34.53504792517542</v>
       </c>
       <c r="I9" t="n">
-        <v>4.734819236021681</v>
+        <v>4.595777350085017</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693117642035831</v>
+        <v>4.692261946355355</v>
       </c>
       <c r="K9" t="n">
-        <v>13.03246091604858</v>
+        <v>15.02177120712996</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88963251583243</v>
+        <v>43.74422830426191</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84245859576941</v>
+        <v>99.84708308916331</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.02453619660915</v>
+        <v>82.64714160793686</v>
       </c>
       <c r="C10" t="n">
-        <v>41.71286725594869</v>
+        <v>39.46235679605509</v>
       </c>
       <c r="D10" t="n">
-        <v>1.861041154009848</v>
+        <v>1.75807440891033</v>
       </c>
       <c r="E10" t="n">
-        <v>10.38634049709519</v>
+        <v>9.837450841411396</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520621726771326</v>
+        <v>0.7519233659743869</v>
       </c>
       <c r="G10" t="n">
-        <v>28.77804820001314</v>
+        <v>27.17595780608479</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59485994314811</v>
+        <v>34.5884748348218</v>
       </c>
       <c r="I10" t="n">
-        <v>3.951795650433636</v>
+        <v>3.835739313394244</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700388579232079</v>
+        <v>4.699521037339918</v>
       </c>
       <c r="K10" t="n">
-        <v>14.97546380339087</v>
+        <v>17.35285839206314</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18014618410428</v>
+        <v>43.05712432993495</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86847724344383</v>
+        <v>99.87233951805318</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.90452165725711</v>
+        <v>80.185781614934</v>
       </c>
       <c r="C11" t="n">
-        <v>40.20633799144797</v>
+        <v>37.59478800068283</v>
       </c>
       <c r="D11" t="n">
-        <v>1.767210623538631</v>
+        <v>1.648655895336766</v>
       </c>
       <c r="E11" t="n">
-        <v>10.41226707513799</v>
+        <v>9.75864089719459</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530592823431654</v>
+        <v>0.7529238271900578</v>
       </c>
       <c r="G11" t="n">
-        <v>27.32710794395516</v>
+        <v>25.48458860520852</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64072698778562</v>
+        <v>34.63449605074265</v>
       </c>
       <c r="I11" t="n">
-        <v>3.297529229851757</v>
+        <v>3.200702419323557</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706620514644785</v>
+        <v>4.705773919937861</v>
       </c>
       <c r="K11" t="n">
-        <v>17.09547834274289</v>
+        <v>19.81421838506598</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58841156440822</v>
+        <v>42.48444529999026</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89022789859908</v>
+        <v>99.89345168573907</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.65813119359737</v>
+        <v>77.72424627004632</v>
       </c>
       <c r="C12" t="n">
-        <v>38.47124463212793</v>
+        <v>35.62781588272606</v>
       </c>
       <c r="D12" t="n">
-        <v>1.668619909435953</v>
+        <v>1.54041478728193</v>
       </c>
       <c r="E12" t="n">
-        <v>10.28988915285964</v>
+        <v>9.562996679386091</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539154535989646</v>
+        <v>0.7537860795488227</v>
       </c>
       <c r="G12" t="n">
-        <v>25.80255900187111</v>
+        <v>23.8114195001504</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68011086555239</v>
+        <v>34.67415965924584</v>
       </c>
       <c r="I12" t="n">
-        <v>2.751065225285774</v>
+        <v>2.670306567253097</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711971584993529</v>
+        <v>4.711162997180142</v>
       </c>
       <c r="K12" t="n">
-        <v>19.34186880640265</v>
+        <v>22.27575372995368</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09528852730686</v>
+        <v>42.00752198678348</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90840196583744</v>
+        <v>99.91109159946322</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.27948155444928</v>
+        <v>75.2950207576533</v>
       </c>
       <c r="C13" t="n">
-        <v>36.51842627101841</v>
+        <v>33.61026744609272</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56503783881307</v>
+        <v>1.43465259030244</v>
       </c>
       <c r="E13" t="n">
-        <v>10.03359469566179</v>
+        <v>9.277659611764722</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546521647916034</v>
+        <v>0.7545293870659265</v>
       </c>
       <c r="G13" t="n">
-        <v>24.20082665187994</v>
+        <v>22.176568899956</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71399958041377</v>
+        <v>34.70835180503262</v>
       </c>
       <c r="I13" t="n">
-        <v>2.294794592941586</v>
+        <v>2.227449794369563</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716576029947522</v>
+        <v>4.71580866916204</v>
       </c>
       <c r="K13" t="n">
-        <v>21.72051844555072</v>
+        <v>24.70497924234669</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68463680495073</v>
+        <v>41.6105781291369</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92358152151985</v>
+        <v>99.92582481757631</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.49427675912588</v>
+        <v>82.69103202839646</v>
       </c>
       <c r="C14" t="n">
-        <v>40.31604361177789</v>
+        <v>38.33638424797918</v>
       </c>
       <c r="D14" t="n">
-        <v>1.566903148496847</v>
+        <v>1.43622734350268</v>
       </c>
       <c r="E14" t="n">
-        <v>12.18052521164287</v>
+        <v>11.86382129645959</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555516062977183</v>
+        <v>0.755357599815821</v>
       </c>
       <c r="G14" t="n">
-        <v>25.86111482001216</v>
+        <v>24.32305812166426</v>
       </c>
       <c r="H14" t="n">
-        <v>36.38681800358805</v>
+        <v>36.86859659750965</v>
       </c>
       <c r="I14" t="n">
-        <v>3.021166429727505</v>
+        <v>2.722986070595578</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72219753936074</v>
+        <v>4.720984998848881</v>
       </c>
       <c r="K14" t="n">
-        <v>15.50572324087412</v>
+        <v>17.30896797160354</v>
       </c>
       <c r="L14" t="n">
-        <v>44.07764748395603</v>
+        <v>44.26398109877596</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89941433660803</v>
+        <v>99.90933331835868</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.68295063885927</v>
+        <v>81.97443474411264</v>
       </c>
       <c r="C15" t="n">
-        <v>39.97237511475625</v>
+        <v>38.04005958696347</v>
       </c>
       <c r="D15" t="n">
-        <v>1.53634803254179</v>
+        <v>1.410173082775649</v>
       </c>
       <c r="E15" t="n">
-        <v>12.36302872029298</v>
+        <v>12.02714431233184</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563100704298993</v>
+        <v>0.756055218339126</v>
       </c>
       <c r="G15" t="n">
-        <v>25.35681475346971</v>
+        <v>23.88181927403513</v>
       </c>
       <c r="H15" t="n">
-        <v>36.42334508672821</v>
+        <v>36.90264698095844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.520166035209796</v>
+        <v>2.271250761052909</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726937940186872</v>
+        <v>4.725345114619537</v>
       </c>
       <c r="K15" t="n">
-        <v>16.31704936114073</v>
+        <v>18.02556525588737</v>
       </c>
       <c r="L15" t="n">
-        <v>43.62665423438838</v>
+        <v>43.85873665518818</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91607871028536</v>
+        <v>99.92436149803902</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.24373956279581</v>
+        <v>79.51189734259628</v>
       </c>
       <c r="C16" t="n">
-        <v>37.92331356111673</v>
+        <v>35.92810598055606</v>
       </c>
       <c r="D16" t="n">
-        <v>1.442128593572894</v>
+        <v>1.318167447012252</v>
       </c>
       <c r="E16" t="n">
-        <v>11.95516760284569</v>
+        <v>11.55814471792022</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569623158037474</v>
+        <v>0.7566556017998546</v>
       </c>
       <c r="G16" t="n">
-        <v>23.80176029347374</v>
+        <v>22.3236687233458</v>
       </c>
       <c r="H16" t="n">
-        <v>36.45475675141672</v>
+        <v>36.93195137350419</v>
       </c>
       <c r="I16" t="n">
-        <v>2.101949531909582</v>
+        <v>1.894211967764872</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731014473773422</v>
+        <v>4.729097511249091</v>
       </c>
       <c r="K16" t="n">
-        <v>18.75626043720419</v>
+        <v>20.48810265740373</v>
       </c>
       <c r="L16" t="n">
-        <v>43.25042138958992</v>
+        <v>43.52070106312206</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92999538791084</v>
+        <v>99.93690970108186</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.70033899663272</v>
+        <v>81.30218300362962</v>
       </c>
       <c r="C17" t="n">
-        <v>38.99528768226419</v>
+        <v>37.23983779908367</v>
       </c>
       <c r="D17" t="n">
-        <v>1.443353135030446</v>
+        <v>1.31916927007058</v>
       </c>
       <c r="E17" t="n">
-        <v>12.66095111105881</v>
+        <v>12.36349390890281</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576050682889541</v>
+        <v>0.7572306691259478</v>
       </c>
       <c r="G17" t="n">
-        <v>24.16649007971871</v>
+        <v>22.82824667404133</v>
       </c>
       <c r="H17" t="n">
-        <v>36.83023046077233</v>
+        <v>37.44763179409813</v>
       </c>
       <c r="I17" t="n">
-        <v>2.106677464957495</v>
+        <v>1.853719005353651</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735031676805964</v>
+        <v>4.732691682037173</v>
       </c>
       <c r="K17" t="n">
-        <v>17.29966100336728</v>
+        <v>18.69781699637037</v>
       </c>
       <c r="L17" t="n">
-        <v>43.63488830907398</v>
+        <v>44.00060149699193</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92983699470545</v>
+        <v>99.93825629244598</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.28680062303532</v>
+        <v>78.95092670438964</v>
       </c>
       <c r="C18" t="n">
-        <v>36.90745511285473</v>
+        <v>35.17434519586647</v>
       </c>
       <c r="D18" t="n">
-        <v>1.353314812771329</v>
+        <v>1.23502192932772</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1639513547391</v>
+        <v>11.83247875348383</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581576683505127</v>
+        <v>0.7577248611212239</v>
       </c>
       <c r="G18" t="n">
-        <v>22.65895171723503</v>
+        <v>21.37207551009371</v>
       </c>
       <c r="H18" t="n">
-        <v>36.85709457305422</v>
+        <v>37.47207126892296</v>
       </c>
       <c r="I18" t="n">
-        <v>1.756845069694419</v>
+        <v>1.545773999432557</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738485427190706</v>
+        <v>4.73578038200765</v>
       </c>
       <c r="K18" t="n">
-        <v>19.71319937696468</v>
+        <v>21.04907329561036</v>
       </c>
       <c r="L18" t="n">
-        <v>43.32082669170955</v>
+        <v>43.72508931393001</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94148118152896</v>
+        <v>99.94850780540682</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.26650950391976</v>
+        <v>78.02969392863261</v>
       </c>
       <c r="C19" t="n">
-        <v>36.15809069366021</v>
+        <v>34.48525559751859</v>
       </c>
       <c r="D19" t="n">
-        <v>1.315956962189546</v>
+        <v>1.202421233845246</v>
       </c>
       <c r="E19" t="n">
-        <v>12.07232569348242</v>
+        <v>11.73583620254714</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586247235607274</v>
+        <v>0.7581437772738755</v>
       </c>
       <c r="G19" t="n">
-        <v>22.03345813318208</v>
+        <v>20.80791991982635</v>
       </c>
       <c r="H19" t="n">
-        <v>36.87980000593755</v>
+        <v>37.49278809733035</v>
       </c>
       <c r="I19" t="n">
-        <v>1.464939463312904</v>
+        <v>1.29418608984793</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741404522254547</v>
+        <v>4.738398607961722</v>
       </c>
       <c r="K19" t="n">
-        <v>20.73349049608022</v>
+        <v>21.9703060713674</v>
       </c>
       <c r="L19" t="n">
-        <v>43.0596175583236</v>
+        <v>43.50132263175328</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95119874806404</v>
+        <v>99.95688430063925</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.63939191726348</v>
+        <v>75.40247816720589</v>
       </c>
       <c r="C20" t="n">
-        <v>33.75671174010748</v>
+        <v>32.05685344010033</v>
       </c>
       <c r="D20" t="n">
-        <v>1.219003876942067</v>
+        <v>1.109338937146523</v>
       </c>
       <c r="E20" t="n">
-        <v>11.38646940484269</v>
+        <v>11.00717092764509</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590277400130148</v>
+        <v>0.7585054096373997</v>
       </c>
       <c r="G20" t="n">
-        <v>20.41014384095108</v>
+        <v>19.19712919096783</v>
       </c>
       <c r="H20" t="n">
-        <v>36.89939225714932</v>
+        <v>37.51067204755349</v>
       </c>
       <c r="I20" t="n">
-        <v>1.221431422283966</v>
+        <v>1.079002844021799</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743923375081343</v>
+        <v>4.740658810233748</v>
       </c>
       <c r="K20" t="n">
-        <v>23.36060808273651</v>
+        <v>24.59752183279411</v>
       </c>
       <c r="L20" t="n">
-        <v>42.84198741428619</v>
+        <v>43.30967511349868</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95930723713019</v>
+        <v>99.96405038639313</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.31619093743799</v>
+        <v>81.28686773944337</v>
       </c>
       <c r="C21" t="n">
-        <v>37.20995595325022</v>
+        <v>35.79999311545396</v>
       </c>
       <c r="D21" t="n">
-        <v>1.219911403300084</v>
+        <v>1.109996125481189</v>
       </c>
       <c r="E21" t="n">
-        <v>13.26708802590208</v>
+        <v>12.99910904719481</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595928224492219</v>
+        <v>0.7589547591466462</v>
       </c>
       <c r="G21" t="n">
-        <v>21.99106584139264</v>
+        <v>20.95314161422793</v>
       </c>
       <c r="H21" t="n">
-        <v>38.49259020506296</v>
+        <v>39.27753367688466</v>
       </c>
       <c r="I21" t="n">
-        <v>1.838487499023375</v>
+        <v>1.444665271841594</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747455140307638</v>
+        <v>4.743467244666539</v>
       </c>
       <c r="K21" t="n">
-        <v>17.68380906256201</v>
+        <v>18.71313226055662</v>
       </c>
       <c r="L21" t="n">
-        <v>45.04499765763666</v>
+        <v>45.43874762605349</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93876267344888</v>
+        <v>99.95187300206408</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_12_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.38539502757816</v>
+        <v>43.37479092169952</v>
       </c>
       <c r="M2" t="n">
-        <v>100.9651976429611</v>
+        <v>96.49400924978198</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92995348875149</v>
+        <v>81.5211182453792</v>
       </c>
       <c r="C3" t="n">
-        <v>45.81838937750821</v>
+        <v>43.27667380093477</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228564356072622</v>
+        <v>2.182787944797178</v>
       </c>
       <c r="E3" t="n">
-        <v>5.638287410281158</v>
+        <v>4.151343828586045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428547853575408</v>
+        <v>0.7376641707228753</v>
       </c>
       <c r="G3" t="n">
-        <v>33.93580570636004</v>
+        <v>32.83276866965756</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17132012644687</v>
+        <v>33.93255185325226</v>
       </c>
       <c r="I3" t="n">
-        <v>6.570278695748642</v>
+        <v>3.073600711345314</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64284240848463</v>
+        <v>4.61040106701797</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07004651124849</v>
+        <v>18.47888175462079</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87570720442901</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641430931857</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91559721641936</v>
+        <v>88.43268141310304</v>
       </c>
       <c r="C4" t="n">
-        <v>42.44369469348207</v>
+        <v>42.75696198009742</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179063109709986</v>
+        <v>2.188482063439958</v>
       </c>
       <c r="E4" t="n">
-        <v>6.427507735370426</v>
+        <v>6.453214488409865</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444179344393389</v>
+        <v>0.7395884746006917</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18201788138312</v>
+        <v>33.48721468451069</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24322498420958</v>
+        <v>34.02106983163181</v>
       </c>
       <c r="I4" t="n">
-        <v>5.48675348106103</v>
+        <v>6.920683904255704</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652612090245868</v>
+        <v>4.622427966254323</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08440278358064</v>
+        <v>11.56731858689695</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28939478138871</v>
+        <v>45.44563019065932</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81749225845142</v>
+        <v>99.76991075765369</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.70177608297827</v>
+        <v>87.17511368959231</v>
       </c>
       <c r="C5" t="n">
-        <v>42.08123462205359</v>
+        <v>42.57213808526377</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119537820637717</v>
+        <v>2.127847242924497</v>
       </c>
       <c r="E5" t="n">
-        <v>7.01533474862184</v>
+        <v>7.237750019697903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457441465148005</v>
+        <v>0.7412230422609021</v>
       </c>
       <c r="G5" t="n">
-        <v>32.27558740785113</v>
+        <v>32.55940664537766</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30423073968082</v>
+        <v>34.09625994400149</v>
       </c>
       <c r="I5" t="n">
-        <v>4.580440303954457</v>
+        <v>5.779982781199218</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660900915717503</v>
+        <v>4.632644014130638</v>
       </c>
       <c r="K5" t="n">
-        <v>14.29822391702174</v>
+        <v>12.82488631040768</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46813164200631</v>
+        <v>44.41073438476588</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84759018108164</v>
+        <v>99.80775878043734</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.17232739430001</v>
+        <v>85.60252295232526</v>
       </c>
       <c r="C6" t="n">
-        <v>41.26292769938537</v>
+        <v>41.89641159927159</v>
       </c>
       <c r="D6" t="n">
-        <v>2.044345300716459</v>
+        <v>2.051880996659941</v>
       </c>
       <c r="E6" t="n">
-        <v>7.403594762568948</v>
+        <v>7.783639093622805</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468731160376505</v>
+        <v>0.742615883809072</v>
       </c>
       <c r="G6" t="n">
-        <v>31.13058177242209</v>
+        <v>31.39700369954817</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35616333773192</v>
+        <v>34.1603306552173</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822812129587634</v>
+        <v>4.825703349661284</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667956975235315</v>
+        <v>4.641349273806699</v>
       </c>
       <c r="K6" t="n">
-        <v>15.82767260569998</v>
+        <v>14.39747704767472</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78216524202703</v>
+        <v>43.54555627579814</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87276554711238</v>
+        <v>99.83944492274446</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.41576277271115</v>
+        <v>83.86186042501747</v>
       </c>
       <c r="C7" t="n">
-        <v>40.09977645926568</v>
+        <v>40.904713722674</v>
       </c>
       <c r="D7" t="n">
-        <v>1.958372882985232</v>
+        <v>1.968405629714091</v>
       </c>
       <c r="E7" t="n">
-        <v>7.62387683841778</v>
+        <v>8.138291882592707</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478366719712022</v>
+        <v>0.7438048037366686</v>
       </c>
       <c r="G7" t="n">
-        <v>29.8214235889113</v>
+        <v>30.11969940700574</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4004869106753</v>
+        <v>34.21502097188674</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189786679930343</v>
+        <v>4.027857706727327</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673979199820013</v>
+        <v>4.648780023354178</v>
       </c>
       <c r="K7" t="n">
-        <v>17.58423722728883</v>
+        <v>16.13813957498255</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2097970876236</v>
+        <v>42.82309938707507</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89381077417812</v>
+        <v>99.86595268473161</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.17023194512251</v>
+        <v>81.82662256401261</v>
       </c>
       <c r="C8" t="n">
-        <v>42.41920636208909</v>
+        <v>39.49438854353429</v>
       </c>
       <c r="D8" t="n">
-        <v>1.962495414150058</v>
+        <v>1.871373770634994</v>
       </c>
       <c r="E8" t="n">
-        <v>9.460739570168862</v>
+        <v>8.297308317047619</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749410927830843</v>
+        <v>0.7448232314462861</v>
       </c>
       <c r="G8" t="n">
-        <v>30.33585626369076</v>
+        <v>28.63495948132801</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47290268021877</v>
+        <v>34.26186864652915</v>
       </c>
       <c r="I8" t="n">
-        <v>5.505008790120442</v>
+        <v>3.361143920487269</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683818298942768</v>
+        <v>4.655145196539288</v>
       </c>
       <c r="K8" t="n">
-        <v>12.82976805487748</v>
+        <v>18.17337743598738</v>
       </c>
       <c r="L8" t="n">
-        <v>44.56791076133864</v>
+        <v>42.22034908418036</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81688517830523</v>
+        <v>99.88811506370203</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.97822879287004</v>
+        <v>79.70264948215952</v>
       </c>
       <c r="C9" t="n">
-        <v>41.08108357777144</v>
+        <v>37.89131726311592</v>
       </c>
       <c r="D9" t="n">
-        <v>1.862832949828227</v>
+        <v>1.771016038005178</v>
       </c>
       <c r="E9" t="n">
-        <v>9.746252615663209</v>
+        <v>8.319714630146365</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750761911416857</v>
+        <v>0.7456967539589493</v>
       </c>
       <c r="G9" t="n">
-        <v>28.79529409434595</v>
+        <v>27.0993284638442</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53504792517542</v>
+        <v>34.30205068211166</v>
       </c>
       <c r="I9" t="n">
-        <v>4.595777350085017</v>
+        <v>2.804238201849738</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692261946355355</v>
+        <v>4.660604712243432</v>
       </c>
       <c r="K9" t="n">
-        <v>15.02177120712996</v>
+        <v>20.29735051784049</v>
       </c>
       <c r="L9" t="n">
-        <v>43.74422830426191</v>
+        <v>41.71796711014116</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84708308916331</v>
+        <v>99.90663489109757</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.64714160793686</v>
+        <v>84.98696684450212</v>
       </c>
       <c r="C10" t="n">
-        <v>39.46235679605509</v>
+        <v>41.50711466793015</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75807440891033</v>
+        <v>1.773015528387543</v>
       </c>
       <c r="E10" t="n">
-        <v>9.837450841411396</v>
+        <v>10.35668039329837</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519233659743869</v>
+        <v>0.7465386511838782</v>
       </c>
       <c r="G10" t="n">
-        <v>27.17595780608479</v>
+        <v>28.6777419386559</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5884748348218</v>
+        <v>35.88859608429907</v>
       </c>
       <c r="I10" t="n">
-        <v>3.835739313394244</v>
+        <v>2.878527678778118</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699521037339918</v>
+        <v>4.665866569899238</v>
       </c>
       <c r="K10" t="n">
-        <v>17.35285839206314</v>
+        <v>15.01303315549786</v>
       </c>
       <c r="L10" t="n">
-        <v>43.05712432993495</v>
+        <v>43.38400946109028</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87233951805318</v>
+        <v>99.90415728451829</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.185781614934</v>
+        <v>84.49399205229165</v>
       </c>
       <c r="C11" t="n">
-        <v>37.59478800068283</v>
+        <v>41.4020729004963</v>
       </c>
       <c r="D11" t="n">
-        <v>1.648655895336766</v>
+        <v>1.749134646947162</v>
       </c>
       <c r="E11" t="n">
-        <v>9.75864089719459</v>
+        <v>10.63928429776685</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529238271900578</v>
+        <v>0.747258330218058</v>
       </c>
       <c r="G11" t="n">
-        <v>25.48458860520852</v>
+        <v>28.30630809867038</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63449605074265</v>
+        <v>35.93802230367241</v>
       </c>
       <c r="I11" t="n">
-        <v>3.200702419323557</v>
+        <v>2.443619811153936</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705773919937861</v>
+        <v>4.670364563862862</v>
       </c>
       <c r="K11" t="n">
-        <v>19.81421838506598</v>
+        <v>15.50600794770835</v>
       </c>
       <c r="L11" t="n">
-        <v>42.48444529999026</v>
+        <v>43.01054360583597</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89345168573907</v>
+        <v>99.91862445404062</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.72424627004632</v>
+        <v>82.40634482911898</v>
       </c>
       <c r="C12" t="n">
-        <v>35.62781588272606</v>
+        <v>39.69372979086782</v>
       </c>
       <c r="D12" t="n">
-        <v>1.54041478728193</v>
+        <v>1.660771689599376</v>
       </c>
       <c r="E12" t="n">
-        <v>9.562996679386091</v>
+        <v>10.44147930849022</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537860795488227</v>
+        <v>0.7478743563387789</v>
       </c>
       <c r="G12" t="n">
-        <v>23.8114195001504</v>
+        <v>26.87632722237731</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67415965924584</v>
+        <v>35.96764895294596</v>
       </c>
       <c r="I12" t="n">
-        <v>2.670306567253097</v>
+        <v>2.03802857224996</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711162997180142</v>
+        <v>4.674214727117368</v>
       </c>
       <c r="K12" t="n">
-        <v>22.27575372995368</v>
+        <v>17.59365517088103</v>
       </c>
       <c r="L12" t="n">
-        <v>42.00752198678348</v>
+        <v>42.64473671016356</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91109159946322</v>
+        <v>99.9321216719124</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.2950207576533</v>
+        <v>83.6203347702824</v>
       </c>
       <c r="C13" t="n">
-        <v>33.61026744609272</v>
+        <v>40.69788304768524</v>
       </c>
       <c r="D13" t="n">
-        <v>1.43465259030244</v>
+        <v>1.662023429389393</v>
       </c>
       <c r="E13" t="n">
-        <v>9.277659611764722</v>
+        <v>11.09299412772859</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545293870659265</v>
+        <v>0.7484380365216871</v>
       </c>
       <c r="G13" t="n">
-        <v>22.176568899956</v>
+        <v>27.22510184469136</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70835180503262</v>
+        <v>36.3232757929521</v>
       </c>
       <c r="I13" t="n">
-        <v>2.227449794369563</v>
+        <v>1.890763810738737</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71580866916204</v>
+        <v>4.677737728260545</v>
       </c>
       <c r="K13" t="n">
-        <v>24.70497924234669</v>
+        <v>16.37966522971759</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6105781291369</v>
+        <v>42.8594737293658</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92582481757631</v>
+        <v>99.93702200676863</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.69103202839646</v>
+        <v>81.52233992630697</v>
       </c>
       <c r="C14" t="n">
-        <v>38.33638424797918</v>
+        <v>38.89316867918041</v>
       </c>
       <c r="D14" t="n">
-        <v>1.43622734350268</v>
+        <v>1.575822399235926</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86382129645959</v>
+        <v>10.78043013192221</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755357599815821</v>
+        <v>0.7489205327039999</v>
       </c>
       <c r="G14" t="n">
-        <v>24.32305812166426</v>
+        <v>25.81306890728106</v>
       </c>
       <c r="H14" t="n">
-        <v>36.86859659750965</v>
+        <v>36.34669234989335</v>
       </c>
       <c r="I14" t="n">
-        <v>2.722986070595578</v>
+        <v>1.576652275870434</v>
       </c>
       <c r="J14" t="n">
-        <v>4.720984998848881</v>
+        <v>4.680753329400001</v>
       </c>
       <c r="K14" t="n">
-        <v>17.30896797160354</v>
+        <v>18.47766007369303</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26398109877596</v>
+        <v>42.57665003016159</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90933331835868</v>
+        <v>99.94747878303504</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.97443474411264</v>
+        <v>80.60666384255597</v>
       </c>
       <c r="C15" t="n">
-        <v>38.04005958696347</v>
+        <v>38.19769680946195</v>
       </c>
       <c r="D15" t="n">
-        <v>1.410173082775649</v>
+        <v>1.53772543732287</v>
       </c>
       <c r="E15" t="n">
-        <v>12.02714431233184</v>
+        <v>10.74275256412983</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756055218339126</v>
+        <v>0.7493348192929061</v>
       </c>
       <c r="G15" t="n">
-        <v>23.88181927403513</v>
+        <v>25.18901412579261</v>
       </c>
       <c r="H15" t="n">
-        <v>36.90264698095844</v>
+        <v>36.36679855146495</v>
       </c>
       <c r="I15" t="n">
-        <v>2.271250761052909</v>
+        <v>1.337695723972149</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725345114619537</v>
+        <v>4.683342620580665</v>
       </c>
       <c r="K15" t="n">
-        <v>18.02556525588737</v>
+        <v>19.39333615744403</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85873665518818</v>
+        <v>42.36440182813271</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92436149803902</v>
+        <v>99.95543479503868</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.51189734259628</v>
+        <v>78.23031407199542</v>
       </c>
       <c r="C16" t="n">
-        <v>35.92810598055606</v>
+        <v>36.02826824875159</v>
       </c>
       <c r="D16" t="n">
-        <v>1.318167447012252</v>
+        <v>1.440885869920669</v>
       </c>
       <c r="E16" t="n">
-        <v>11.55814471792022</v>
+        <v>10.25209794629206</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7566556017998546</v>
+        <v>0.7496909111232373</v>
       </c>
       <c r="G16" t="n">
-        <v>22.3236687233458</v>
+        <v>23.60271453548576</v>
       </c>
       <c r="H16" t="n">
-        <v>36.93195137350419</v>
+        <v>36.3840804387149</v>
       </c>
       <c r="I16" t="n">
-        <v>1.894211967764872</v>
+        <v>1.115276175938575</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729097511249091</v>
+        <v>4.685568194520235</v>
       </c>
       <c r="K16" t="n">
-        <v>20.48810265740373</v>
+        <v>21.76968592800456</v>
       </c>
       <c r="L16" t="n">
-        <v>43.52070106312206</v>
+        <v>42.16488760868908</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93690970108186</v>
+        <v>99.96284178544524</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.30218300362962</v>
+        <v>83.25916942484409</v>
       </c>
       <c r="C17" t="n">
-        <v>37.23983779908367</v>
+        <v>39.33519159281052</v>
       </c>
       <c r="D17" t="n">
-        <v>1.31916927007058</v>
+        <v>1.441620644444202</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36349390890281</v>
+        <v>12.00921022154056</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572306691259478</v>
+        <v>0.750073213284371</v>
       </c>
       <c r="G17" t="n">
-        <v>22.82824667404133</v>
+        <v>25.15434635183251</v>
       </c>
       <c r="H17" t="n">
-        <v>37.44763179409813</v>
+        <v>37.94223006624829</v>
       </c>
       <c r="I17" t="n">
-        <v>1.853719005353651</v>
+        <v>1.273731344466834</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732691682037173</v>
+        <v>4.687957583027321</v>
       </c>
       <c r="K17" t="n">
-        <v>18.69781699637037</v>
+        <v>16.74083057515591</v>
       </c>
       <c r="L17" t="n">
-        <v>44.00060149699193</v>
+        <v>43.88154176067201</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93825629244598</v>
+        <v>99.95756392863845</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.95092670438964</v>
+        <v>84.92252492519538</v>
       </c>
       <c r="C18" t="n">
-        <v>35.17434519586647</v>
+        <v>40.06225837110881</v>
       </c>
       <c r="D18" t="n">
-        <v>1.23502192932772</v>
+        <v>1.442842879337219</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83247875348383</v>
+        <v>12.61112847396598</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577248611212239</v>
+        <v>0.7507091403967682</v>
       </c>
       <c r="G18" t="n">
-        <v>21.37207551009371</v>
+        <v>25.29154346347542</v>
       </c>
       <c r="H18" t="n">
-        <v>37.47207126892296</v>
+        <v>37.97439824980238</v>
       </c>
       <c r="I18" t="n">
-        <v>1.545773999432557</v>
+        <v>2.159970590737809</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73578038200765</v>
+        <v>4.691932127479802</v>
       </c>
       <c r="K18" t="n">
-        <v>21.04907329561036</v>
+        <v>15.07747507480462</v>
       </c>
       <c r="L18" t="n">
-        <v>43.72508931393001</v>
+        <v>44.78832852489911</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94850780540682</v>
+        <v>99.92806197081254</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.02969392863261</v>
+        <v>82.22034290907237</v>
       </c>
       <c r="C19" t="n">
-        <v>34.48525559751859</v>
+        <v>37.69403785643264</v>
       </c>
       <c r="D19" t="n">
-        <v>1.202421233845246</v>
+        <v>1.344732222022258</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73583620254714</v>
+        <v>12.05380996731796</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581437772738755</v>
+        <v>0.7512573602934831</v>
       </c>
       <c r="G19" t="n">
-        <v>20.80791991982635</v>
+        <v>23.57176510836352</v>
       </c>
       <c r="H19" t="n">
-        <v>37.49278809733035</v>
+        <v>38.00212978997693</v>
       </c>
       <c r="I19" t="n">
-        <v>1.29418608984793</v>
+        <v>1.801289959263948</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738398607961722</v>
+        <v>4.695358501834271</v>
       </c>
       <c r="K19" t="n">
-        <v>21.9703060713674</v>
+        <v>17.77965709092763</v>
       </c>
       <c r="L19" t="n">
-        <v>43.50132263175328</v>
+        <v>44.46630586956368</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95688430063925</v>
+        <v>99.94000081692394</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.40247816720589</v>
+        <v>79.46787577553786</v>
       </c>
       <c r="C20" t="n">
-        <v>32.05685344010033</v>
+        <v>35.21927668547157</v>
       </c>
       <c r="D20" t="n">
-        <v>1.109338937146523</v>
+        <v>1.245400047197129</v>
       </c>
       <c r="E20" t="n">
-        <v>11.00717092764509</v>
+        <v>11.41376044094477</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585054096373997</v>
+        <v>0.7517306769594466</v>
       </c>
       <c r="G20" t="n">
-        <v>19.19712919096783</v>
+        <v>21.83057481461143</v>
       </c>
       <c r="H20" t="n">
-        <v>37.51067204755349</v>
+        <v>38.02607237253569</v>
       </c>
       <c r="I20" t="n">
-        <v>1.079002844021799</v>
+        <v>1.502020692292852</v>
       </c>
       <c r="J20" t="n">
-        <v>4.740658810233748</v>
+        <v>4.698316730996543</v>
       </c>
       <c r="K20" t="n">
-        <v>24.59752183279411</v>
+        <v>20.53212422446216</v>
       </c>
       <c r="L20" t="n">
-        <v>43.30967511349868</v>
+        <v>44.19856325786449</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96405038639313</v>
+        <v>99.94996416779821</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.28686773944337</v>
+        <v>76.60487366798216</v>
       </c>
       <c r="C21" t="n">
-        <v>35.79999311545396</v>
+        <v>32.58707785719777</v>
       </c>
       <c r="D21" t="n">
-        <v>1.109996125481189</v>
+        <v>1.142641396722465</v>
       </c>
       <c r="E21" t="n">
-        <v>12.99910904719481</v>
+        <v>10.68073238808289</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7589547591466462</v>
+        <v>0.7521403297242918</v>
       </c>
       <c r="G21" t="n">
-        <v>20.95314161422793</v>
+        <v>20.02932194643921</v>
       </c>
       <c r="H21" t="n">
-        <v>39.27753367688466</v>
+        <v>38.04679453562024</v>
       </c>
       <c r="I21" t="n">
-        <v>1.444665271841594</v>
+        <v>1.252366010616238</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743467244666539</v>
+        <v>4.700877060776825</v>
       </c>
       <c r="K21" t="n">
-        <v>18.71313226055662</v>
+        <v>23.39512633201783</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43874762605349</v>
+        <v>43.97607301377628</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95187300206408</v>
+        <v>99.95827720299189</v>
       </c>
     </row>
   </sheetData>
